--- a/research/traditional_assets/database/data/spain/spain_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_heathcare_information_and_technology.xlsx
@@ -588,37 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0357</v>
-      </c>
-      <c r="F2">
-        <v>0.355</v>
+        <v>0.03185</v>
       </c>
       <c r="G2">
-        <v>0.107426597582038</v>
+        <v>0.1696649029982363</v>
       </c>
       <c r="H2">
-        <v>-0.1679620034542314</v>
+        <v>-0.02645502645502645</v>
       </c>
       <c r="I2">
-        <v>-0.1328346185856214</v>
+        <v>-0.1330512123253266</v>
       </c>
       <c r="J2">
-        <v>-0.1328346185856214</v>
+        <v>-0.1330512123253266</v>
       </c>
       <c r="K2">
-        <v>-1.801</v>
+        <v>-1.948</v>
       </c>
       <c r="L2">
-        <v>-0.1555267702936097</v>
+        <v>-0.1717813051146384</v>
       </c>
       <c r="M2">
-        <v>0.106</v>
+        <v>0.2</v>
       </c>
       <c r="N2">
-        <v>0.00225531914893617</v>
+        <v>0.003355704697986577</v>
       </c>
       <c r="O2">
-        <v>-0.05885619100499722</v>
+        <v>-0.1026694045174538</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.106</v>
+        <v>0.2</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>7.25</v>
+        <v>15.14</v>
       </c>
       <c r="V2">
-        <v>0.1542553191489362</v>
+        <v>0.2540268456375839</v>
       </c>
       <c r="W2">
-        <v>-0.1078970068672285</v>
+        <v>-0.06447735191637631</v>
       </c>
       <c r="X2">
-        <v>0.09269759920450285</v>
+        <v>0.1845459653285379</v>
       </c>
       <c r="Y2">
-        <v>-0.2005946060717314</v>
+        <v>-0.2490233172449142</v>
       </c>
       <c r="Z2">
-        <v>0.4993720242389306</v>
+        <v>0.3994504387796794</v>
       </c>
       <c r="AA2">
-        <v>-0.06115553425546165</v>
+        <v>-0.04714232180578587</v>
       </c>
       <c r="AB2">
-        <v>0.07373652188255868</v>
+        <v>0.1475017874938506</v>
       </c>
       <c r="AC2">
-        <v>-0.1348920561380203</v>
+        <v>-0.1946441092996364</v>
       </c>
       <c r="AD2">
-        <v>10.77</v>
+        <v>8.1</v>
       </c>
       <c r="AE2">
-        <v>0.5761244161074791</v>
+        <v>0.4090037388460165</v>
       </c>
       <c r="AF2">
-        <v>11.34612441610748</v>
+        <v>8.509003738846017</v>
       </c>
       <c r="AG2">
-        <v>4.096124416107479</v>
+        <v>-6.630996261153983</v>
       </c>
       <c r="AH2">
-        <v>0.1944623491217727</v>
+        <v>0.1249321421800933</v>
       </c>
       <c r="AI2">
-        <v>0.3130300024867033</v>
+        <v>0.1948968828914218</v>
       </c>
       <c r="AJ2">
-        <v>0.08016507050026325</v>
+        <v>-0.1251863503766636</v>
       </c>
       <c r="AK2">
-        <v>0.1412645482315583</v>
+        <v>-0.2325114973115922</v>
       </c>
       <c r="AL2">
-        <v>0.373</v>
+        <v>0.406</v>
       </c>
       <c r="AM2">
-        <v>0.371</v>
+        <v>0.23</v>
       </c>
       <c r="AN2">
-        <v>-5.4039136979428</v>
+        <v>-7.894736842105263</v>
       </c>
       <c r="AO2">
-        <v>-4.812332439678284</v>
+        <v>-4.347290640394089</v>
       </c>
       <c r="AP2">
-        <v>-2.05525560266306</v>
+        <v>6.462959318863532</v>
       </c>
       <c r="AQ2">
-        <v>-4.838274932614556</v>
+        <v>-7.673913043478262</v>
       </c>
     </row>
     <row r="3">
@@ -722,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0115</v>
+        <v>0.0234</v>
       </c>
       <c r="G3">
-        <v>0.1023376623376623</v>
+        <v>0.1073059360730594</v>
       </c>
       <c r="H3">
-        <v>-0.03246753246753246</v>
+        <v>0.00136986301369863</v>
       </c>
       <c r="I3">
-        <v>-0.08496188396721174</v>
+        <v>-0.0483664433064237</v>
       </c>
       <c r="J3">
-        <v>-0.08496188396721174</v>
+        <v>-0.0483664433064237</v>
       </c>
       <c r="K3">
-        <v>-0.461</v>
+        <v>-0.208</v>
       </c>
       <c r="L3">
-        <v>-0.1197402597402597</v>
+        <v>-0.04748858447488585</v>
       </c>
       <c r="M3">
-        <v>0.106</v>
+        <v>0.173</v>
       </c>
       <c r="N3">
-        <v>0.01536231884057971</v>
+        <v>0.02790322580645161</v>
       </c>
       <c r="O3">
-        <v>-0.2299349240780911</v>
+        <v>-0.8317307692307692</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,79 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.106</v>
+        <v>0.173</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V3">
-        <v>0.3304347826086956</v>
+        <v>0.3612903225806452</v>
       </c>
       <c r="W3">
-        <v>-0.06105960264900662</v>
+        <v>-0.02285714285714286</v>
       </c>
       <c r="X3">
-        <v>0.1063974042645403</v>
+        <v>0.2139268956640379</v>
       </c>
       <c r="Y3">
-        <v>-0.167457006913547</v>
+        <v>-0.2367840385211807</v>
       </c>
       <c r="Z3">
-        <v>0.4150712358684911</v>
+        <v>0.3921489590805867</v>
       </c>
       <c r="AA3">
-        <v>-0.03526523417998592</v>
+        <v>-0.01896685039704427</v>
       </c>
       <c r="AB3">
-        <v>0.07435251991026889</v>
+        <v>0.1460687696774978</v>
       </c>
       <c r="AC3">
-        <v>-0.1096177540902548</v>
+        <v>-0.1650356200745421</v>
       </c>
       <c r="AD3">
-        <v>5.2</v>
+        <v>4.63</v>
       </c>
       <c r="AE3">
-        <v>0.2055162663688259</v>
+        <v>0.189225108410679</v>
       </c>
       <c r="AF3">
-        <v>5.405516266368826</v>
+        <v>4.819225108410679</v>
       </c>
       <c r="AG3">
-        <v>3.125516266368826</v>
+        <v>2.579225108410679</v>
       </c>
       <c r="AH3">
-        <v>0.4392758620897677</v>
+        <v>0.4373470058917567</v>
       </c>
       <c r="AI3">
-        <v>0.3887317926801706</v>
+        <v>0.3631881341251811</v>
       </c>
       <c r="AJ3">
-        <v>0.3117561413623706</v>
+        <v>0.2937873304945476</v>
       </c>
       <c r="AK3">
-        <v>0.2688496746944956</v>
+        <v>0.2338537007866319</v>
       </c>
       <c r="AL3">
-        <v>0.101</v>
+        <v>0.108</v>
       </c>
       <c r="AM3">
-        <v>0.101</v>
+        <v>-0.06799999999999999</v>
       </c>
       <c r="AN3">
-        <v>-41.26984126984127</v>
+        <v>43.27102803738318</v>
       </c>
       <c r="AO3">
-        <v>-3.712871287128713</v>
+        <v>-2.546296296296297</v>
       </c>
       <c r="AP3">
-        <v>-24.80568465372084</v>
+        <v>24.10490755523999</v>
       </c>
       <c r="AQ3">
-        <v>-3.712871287128713</v>
+        <v>4.044117647058824</v>
       </c>
     </row>
     <row r="4">
@@ -853,37 +850,34 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0599</v>
-      </c>
-      <c r="F4">
-        <v>0.355</v>
+        <v>0.0403</v>
       </c>
       <c r="G4">
-        <v>0.1099611901681759</v>
+        <v>0.2089080459770115</v>
       </c>
       <c r="H4">
-        <v>-0.2354463130659767</v>
+        <v>-0.04396551724137931</v>
       </c>
       <c r="I4">
-        <v>-0.1566780892558513</v>
+        <v>-0.1863442135182569</v>
       </c>
       <c r="J4">
-        <v>-0.1566780892558513</v>
+        <v>-0.1863442135182569</v>
       </c>
       <c r="K4">
-        <v>-1.34</v>
+        <v>-1.74</v>
       </c>
       <c r="L4">
-        <v>-0.1733505821474774</v>
+        <v>-0.25</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.027</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0005056179775280899</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.01551724137931034</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -895,76 +889,79 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.027</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>4.97</v>
+        <v>12.9</v>
       </c>
       <c r="V4">
-        <v>0.1239401496259352</v>
+        <v>0.2415730337078652</v>
       </c>
       <c r="W4">
-        <v>-0.1547344110854504</v>
+        <v>-0.1060975609756098</v>
       </c>
       <c r="X4">
-        <v>0.07899779414446537</v>
+        <v>0.1551650349930379</v>
       </c>
       <c r="Y4">
-        <v>-0.2337322052299157</v>
+        <v>-0.2612625959686477</v>
       </c>
       <c r="Z4">
-        <v>0.5555712017191743</v>
+        <v>0.4041863806366507</v>
       </c>
       <c r="AA4">
-        <v>-0.08704583433093738</v>
+        <v>-0.07531779321452747</v>
       </c>
       <c r="AB4">
-        <v>0.07312052385484846</v>
+        <v>0.1489348053102033</v>
       </c>
       <c r="AC4">
-        <v>-0.1601663581857858</v>
+        <v>-0.2242525985247308</v>
       </c>
       <c r="AD4">
-        <v>5.57</v>
+        <v>3.47</v>
       </c>
       <c r="AE4">
-        <v>0.3706081497386532</v>
+        <v>0.2197786304353375</v>
       </c>
       <c r="AF4">
-        <v>5.940608149738654</v>
+        <v>3.689778630435338</v>
       </c>
       <c r="AG4">
-        <v>0.9706081497386538</v>
+        <v>-9.210221369564662</v>
       </c>
       <c r="AH4">
-        <v>0.1290297497899661</v>
+        <v>0.06463116023484222</v>
       </c>
       <c r="AI4">
-        <v>0.2659107625862973</v>
+        <v>0.1214151203701111</v>
       </c>
       <c r="AJ4">
-        <v>0.02363267050246565</v>
+        <v>-0.2084242477562719</v>
       </c>
       <c r="AK4">
-        <v>0.05587646335532916</v>
+        <v>-0.526605943058492</v>
       </c>
       <c r="AL4">
-        <v>0.272</v>
+        <v>0.298</v>
       </c>
       <c r="AM4">
-        <v>0.27</v>
+        <v>0.298</v>
       </c>
       <c r="AN4">
-        <v>-2.983395822174612</v>
+        <v>-3.062665489849956</v>
       </c>
       <c r="AO4">
-        <v>-5.220588235294117</v>
+        <v>-5</v>
       </c>
       <c r="AP4">
-        <v>-0.5198758166784434</v>
+        <v>8.129056813384521</v>
       </c>
       <c r="AQ4">
-        <v>-5.259259259259259</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_heathcare_information_and_technology.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +588,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03185</v>
+        <v>0.0225</v>
+      </c>
+      <c r="F2">
+        <v>0.362</v>
       </c>
       <c r="G2">
-        <v>0.1696649029982363</v>
+        <v>-0.07962213225371124</v>
       </c>
       <c r="H2">
-        <v>-0.02645502645502645</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="I2">
-        <v>-0.1330512123253266</v>
+        <v>-0.4536670975849307</v>
       </c>
       <c r="J2">
-        <v>-0.1330512123253266</v>
+        <v>-0.4536670975849307</v>
       </c>
       <c r="K2">
-        <v>-1.948</v>
+        <v>-2.95</v>
       </c>
       <c r="L2">
-        <v>-0.1717813051146384</v>
+        <v>-0.398110661268556</v>
       </c>
       <c r="M2">
-        <v>0.2</v>
+        <v>3.27</v>
       </c>
       <c r="N2">
-        <v>0.003355704697986577</v>
+        <v>0.05459098497495826</v>
       </c>
       <c r="O2">
-        <v>-0.1026694045174538</v>
+        <v>-1.108474576271186</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +630,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.2</v>
+        <v>3.27</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>15.14</v>
+        <v>3.85</v>
       </c>
       <c r="V2">
-        <v>0.2540268456375839</v>
+        <v>0.0642737896494157</v>
       </c>
       <c r="W2">
-        <v>-0.06447735191637631</v>
+        <v>-0.1104868913857678</v>
       </c>
       <c r="X2">
-        <v>0.1845459653285379</v>
+        <v>0.1232597936722172</v>
       </c>
       <c r="Y2">
-        <v>-0.2490233172449142</v>
+        <v>-0.233746685057985</v>
       </c>
       <c r="Z2">
-        <v>0.3994504387796794</v>
+        <v>0.4355655183422205</v>
       </c>
       <c r="AA2">
-        <v>-0.04714232180578587</v>
+        <v>-0.1976017445143911</v>
       </c>
       <c r="AB2">
-        <v>0.1475017874938506</v>
+        <v>0.1196748914994975</v>
       </c>
       <c r="AC2">
-        <v>-0.1946441092996364</v>
+        <v>-0.3172766360138886</v>
       </c>
       <c r="AD2">
-        <v>8.1</v>
+        <v>2.55</v>
       </c>
       <c r="AE2">
-        <v>0.4090037388460165</v>
+        <v>0.3983659655216817</v>
       </c>
       <c r="AF2">
-        <v>8.509003738846017</v>
+        <v>2.948365965521682</v>
       </c>
       <c r="AG2">
-        <v>-6.630996261153983</v>
+        <v>-0.9016340344783185</v>
       </c>
       <c r="AH2">
-        <v>0.1249321421800933</v>
+        <v>0.04691237266437669</v>
       </c>
       <c r="AI2">
-        <v>0.1948968828914218</v>
+        <v>0.1196170963075556</v>
       </c>
       <c r="AJ2">
-        <v>-0.1251863503766636</v>
+        <v>-0.01528235604025421</v>
       </c>
       <c r="AK2">
-        <v>-0.2325114973115922</v>
+        <v>-0.04335119576090712</v>
       </c>
       <c r="AL2">
-        <v>0.406</v>
+        <v>0.123</v>
       </c>
       <c r="AM2">
-        <v>0.23</v>
+        <v>-0.153</v>
       </c>
       <c r="AN2">
-        <v>-7.894736842105263</v>
+        <v>-0.7769652650822668</v>
       </c>
       <c r="AO2">
-        <v>-4.347290640394089</v>
+        <v>-28.61788617886179</v>
       </c>
       <c r="AP2">
-        <v>6.462959318863532</v>
+        <v>0.2747209123943688</v>
       </c>
       <c r="AQ2">
-        <v>-7.673913043478262</v>
+        <v>23.00653594771241</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Euroespes, S.A. (BME:EEP)</t>
+          <t>Pangaea Oncology, S.A. (BME:PANG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,34 +722,37 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0234</v>
+        <v>0.0225</v>
+      </c>
+      <c r="F3">
+        <v>0.362</v>
       </c>
       <c r="G3">
-        <v>0.1073059360730594</v>
+        <v>-0.07962213225371124</v>
       </c>
       <c r="H3">
-        <v>0.00136986301369863</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="I3">
-        <v>-0.0483664433064237</v>
+        <v>-0.4536670975849307</v>
       </c>
       <c r="J3">
-        <v>-0.0483664433064237</v>
+        <v>-0.4536670975849307</v>
       </c>
       <c r="K3">
-        <v>-0.208</v>
+        <v>-2.95</v>
       </c>
       <c r="L3">
-        <v>-0.04748858447488585</v>
+        <v>-0.398110661268556</v>
       </c>
       <c r="M3">
-        <v>0.173</v>
+        <v>3.27</v>
       </c>
       <c r="N3">
-        <v>0.02790322580645161</v>
+        <v>0.05459098497495826</v>
       </c>
       <c r="O3">
-        <v>-0.8317307692307692</v>
+        <v>-1.108474576271186</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,210 +764,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.173</v>
+        <v>3.27</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="V3">
-        <v>0.3612903225806452</v>
+        <v>0.0642737896494157</v>
       </c>
       <c r="W3">
-        <v>-0.02285714285714286</v>
+        <v>-0.1104868913857678</v>
       </c>
       <c r="X3">
-        <v>0.2139268956640379</v>
+        <v>0.1232597936722172</v>
       </c>
       <c r="Y3">
-        <v>-0.2367840385211807</v>
+        <v>-0.233746685057985</v>
       </c>
       <c r="Z3">
-        <v>0.3921489590805867</v>
+        <v>0.4355655183422205</v>
       </c>
       <c r="AA3">
-        <v>-0.01896685039704427</v>
+        <v>-0.1976017445143911</v>
       </c>
       <c r="AB3">
-        <v>0.1460687696774978</v>
+        <v>0.1196748914994975</v>
       </c>
       <c r="AC3">
-        <v>-0.1650356200745421</v>
+        <v>-0.3172766360138886</v>
       </c>
       <c r="AD3">
-        <v>4.63</v>
+        <v>2.55</v>
       </c>
       <c r="AE3">
-        <v>0.189225108410679</v>
+        <v>0.3983659655216817</v>
       </c>
       <c r="AF3">
-        <v>4.819225108410679</v>
+        <v>2.948365965521682</v>
       </c>
       <c r="AG3">
-        <v>2.579225108410679</v>
+        <v>-0.9016340344783185</v>
       </c>
       <c r="AH3">
-        <v>0.4373470058917567</v>
+        <v>0.04691237266437669</v>
       </c>
       <c r="AI3">
-        <v>0.3631881341251811</v>
+        <v>0.1196170963075556</v>
       </c>
       <c r="AJ3">
-        <v>0.2937873304945476</v>
+        <v>-0.01528235604025421</v>
       </c>
       <c r="AK3">
-        <v>0.2338537007866319</v>
+        <v>-0.04335119576090712</v>
       </c>
       <c r="AL3">
-        <v>0.108</v>
+        <v>0.123</v>
       </c>
       <c r="AM3">
-        <v>-0.06799999999999999</v>
+        <v>-0.153</v>
       </c>
       <c r="AN3">
-        <v>43.27102803738318</v>
+        <v>-0.7769652650822668</v>
       </c>
       <c r="AO3">
-        <v>-2.546296296296297</v>
+        <v>-28.61788617886179</v>
       </c>
       <c r="AP3">
-        <v>24.10490755523999</v>
+        <v>0.2747209123943688</v>
       </c>
       <c r="AQ3">
-        <v>4.044117647058824</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Pangaea Oncology, S.A. (BME:PANG)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Heathcare Information and Technology</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0403</v>
-      </c>
-      <c r="G4">
-        <v>0.2089080459770115</v>
-      </c>
-      <c r="H4">
-        <v>-0.04396551724137931</v>
-      </c>
-      <c r="I4">
-        <v>-0.1863442135182569</v>
-      </c>
-      <c r="J4">
-        <v>-0.1863442135182569</v>
-      </c>
-      <c r="K4">
-        <v>-1.74</v>
-      </c>
-      <c r="L4">
-        <v>-0.25</v>
-      </c>
-      <c r="M4">
-        <v>0.027</v>
-      </c>
-      <c r="N4">
-        <v>0.0005056179775280899</v>
-      </c>
-      <c r="O4">
-        <v>-0.01551724137931034</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0.027</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
-        <v>12.9</v>
-      </c>
-      <c r="V4">
-        <v>0.2415730337078652</v>
-      </c>
-      <c r="W4">
-        <v>-0.1060975609756098</v>
-      </c>
-      <c r="X4">
-        <v>0.1551650349930379</v>
-      </c>
-      <c r="Y4">
-        <v>-0.2612625959686477</v>
-      </c>
-      <c r="Z4">
-        <v>0.4041863806366507</v>
-      </c>
-      <c r="AA4">
-        <v>-0.07531779321452747</v>
-      </c>
-      <c r="AB4">
-        <v>0.1489348053102033</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2242525985247308</v>
-      </c>
-      <c r="AD4">
-        <v>3.47</v>
-      </c>
-      <c r="AE4">
-        <v>0.2197786304353375</v>
-      </c>
-      <c r="AF4">
-        <v>3.689778630435338</v>
-      </c>
-      <c r="AG4">
-        <v>-9.210221369564662</v>
-      </c>
-      <c r="AH4">
-        <v>0.06463116023484222</v>
-      </c>
-      <c r="AI4">
-        <v>0.1214151203701111</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.2084242477562719</v>
-      </c>
-      <c r="AK4">
-        <v>-0.526605943058492</v>
-      </c>
-      <c r="AL4">
-        <v>0.298</v>
-      </c>
-      <c r="AM4">
-        <v>0.298</v>
-      </c>
-      <c r="AN4">
-        <v>-3.062665489849956</v>
-      </c>
-      <c r="AO4">
-        <v>-5</v>
-      </c>
-      <c r="AP4">
-        <v>8.129056813384521</v>
-      </c>
-      <c r="AQ4">
-        <v>-5</v>
+        <v>23.00653594771241</v>
       </c>
     </row>
   </sheetData>
